--- a/data/trans_orig/P32-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2007</t>
+          <t>Población según si han pensado que deberían beber menos en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28662</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448449</t>
+          <t>447485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>463274</t>
+          <t>462848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156418</t>
+          <t>156477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609866</t>
+          <t>610015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628278</t>
+          <t>628837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16359</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28556</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52595</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1019018</t>
+          <t>1018205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1039730</t>
+          <t>1038568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517495</t>
+          <t>516415</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529580</t>
+          <t>529082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1540663</t>
+          <t>1540793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1564702</t>
+          <t>1565407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334998</t>
+          <t>334136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347893</t>
+          <t>347447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188043</t>
+          <t>187872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526229</t>
+          <t>526658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>539739</t>
+          <t>540163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>66093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50238</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1811369</t>
+          <t>1814811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1841713</t>
+          <t>1841980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871892</t>
+          <t>871725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887622</t>
+          <t>887473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2693384</t>
+          <t>2692122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2725248</t>
+          <t>2724698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2012</t>
+          <t>Población según si han pensado que deberían beber menos en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22246</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49315</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465576</t>
+          <t>466213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489372</t>
+          <t>490127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220885</t>
+          <t>220168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228162</t>
+          <t>228153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691447</t>
+          <t>691536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>717320</t>
+          <t>717164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69621</t>
+          <t>68732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105466</t>
+          <t>106096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81005</t>
+          <t>82774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121671</t>
+          <t>122306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1091677</t>
+          <t>1091047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1127522</t>
+          <t>1128411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573190</t>
+          <t>573941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589360</t>
+          <t>589321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1672530</t>
+          <t>1671895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1713196</t>
+          <t>1711427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31656</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>38443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294540</t>
+          <t>295175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314379</t>
+          <t>314853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>209981</t>
+          <t>210487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222810</t>
+          <t>222812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>511970</t>
+          <t>512360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>535410</t>
+          <t>534963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115136</t>
+          <t>116677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163765</t>
+          <t>164265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>34593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135448</t>
+          <t>135743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189165</t>
+          <t>187385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1871192</t>
+          <t>1870692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1919821</t>
+          <t>1918280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1015720</t>
+          <t>1016215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036542</t>
+          <t>1036945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2896600</t>
+          <t>2898380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2950317</t>
+          <t>2950022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2016</t>
+          <t>Población según si han pensado que deberían beber menos en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>327048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345235</t>
+          <t>345596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129201</t>
+          <t>129768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461036</t>
+          <t>460893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480139</t>
+          <t>479735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48641</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80174</t>
+          <t>82047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72905</t>
+          <t>72668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113740</t>
+          <t>110002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1172983</t>
+          <t>1171110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1204516</t>
+          <t>1203239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>689349</t>
+          <t>687801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>709867</t>
+          <t>708925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1866224</t>
+          <t>1869962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1907059</t>
+          <t>1907296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44650</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345402</t>
+          <t>345457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>365717</t>
+          <t>365920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262922</t>
+          <t>264300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277944</t>
+          <t>277441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616979</t>
+          <t>616947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639753</t>
+          <t>640389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86101</t>
+          <t>84063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128036</t>
+          <t>125061</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50088</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119857</t>
+          <t>120345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168065</t>
+          <t>167765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1861481</t>
+          <t>1864456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1903416</t>
+          <t>1905454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1094179</t>
+          <t>1093784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1117797</t>
+          <t>1118134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2965719</t>
+          <t>2966019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3013927</t>
+          <t>3013439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han pensado que deberían beber menos en 2023</t>
+          <t>Población según si han pensado que deberían beber menos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214038</t>
+          <t>214945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231256</t>
+          <t>231769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280985</t>
+          <t>280936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297835</t>
+          <t>298100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,82 +5900,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14472</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5684</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26820</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>71132</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>47026</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>96203</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14472</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25969</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>71132</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>43139</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>92842</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>905758</t>
+          <t>905250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>943548</t>
+          <t>943913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,82 +6013,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>693978</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>681630</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>702766</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1622211</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1597140</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1646317</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>95,8%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>693978</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>682481</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>702881</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1622211</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1600501</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1650204</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45640</t>
+          <t>43881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311721</t>
+          <t>311679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330088</t>
+          <t>329885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228420</t>
+          <t>228756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241700</t>
+          <t>241366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>544783</t>
+          <t>546542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>567960</t>
+          <t>568827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76584</t>
+          <t>78868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120680</t>
+          <t>122793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36355</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91466</t>
+          <t>90399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150336</t>
+          <t>151778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1452424</t>
+          <t>1450311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1496520</t>
+          <t>1494236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>985598</t>
+          <t>984560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010794</t>
+          <t>1009602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2444721</t>
+          <t>2443279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2503591</t>
+          <t>2504658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447485</t>
+          <t>447130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462848</t>
+          <t>463477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156477</t>
+          <t>156704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>610015</t>
+          <t>609147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628837</t>
+          <t>628083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1018205</t>
+          <t>1017537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1038568</t>
+          <t>1038583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516415</t>
+          <t>517647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>529082</t>
+          <t>529893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1540793</t>
+          <t>1540155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1565407</t>
+          <t>1565367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334136</t>
+          <t>333466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347447</t>
+          <t>347408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187872</t>
+          <t>188441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526658</t>
+          <t>526493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>540163</t>
+          <t>540045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66093</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1814811</t>
+          <t>1812984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1841980</t>
+          <t>1841871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871725</t>
+          <t>872331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887473</t>
+          <t>887415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2692122</t>
+          <t>2693910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2724698</t>
+          <t>2725490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49226</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466213</t>
+          <t>466967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490127</t>
+          <t>491369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220168</t>
+          <t>220882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228153</t>
+          <t>229144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691536</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>717164</t>
+          <t>716104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68732</t>
+          <t>67975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>106587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82774</t>
+          <t>81616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122306</t>
+          <t>121080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1091047</t>
+          <t>1090556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1128411</t>
+          <t>1129168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573941</t>
+          <t>573096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589321</t>
+          <t>589174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1671895</t>
+          <t>1673121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1711427</t>
+          <t>1712585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295175</t>
+          <t>295147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314853</t>
+          <t>315190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210487</t>
+          <t>210920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222812</t>
+          <t>222817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>512360</t>
+          <t>512437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>534963</t>
+          <t>535205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116677</t>
+          <t>114752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164265</t>
+          <t>162529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135743</t>
+          <t>135132</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187385</t>
+          <t>187268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1870692</t>
+          <t>1872428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1918280</t>
+          <t>1920205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1016215</t>
+          <t>1014989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036945</t>
+          <t>1037069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2898380</t>
+          <t>2898497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2950022</t>
+          <t>2950633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>31273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327048</t>
+          <t>326617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>345596</t>
+          <t>345716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129768</t>
+          <t>130456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460893</t>
+          <t>460917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>479735</t>
+          <t>479362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82047</t>
+          <t>80671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39007</t>
+          <t>39048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72668</t>
+          <t>70537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110002</t>
+          <t>109979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1171110</t>
+          <t>1172486</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1203239</t>
+          <t>1203583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>687801</t>
+          <t>687760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>708925</t>
+          <t>709700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1869962</t>
+          <t>1869985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1907296</t>
+          <t>1909427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44682</t>
+          <t>45119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345457</t>
+          <t>345345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>365920</t>
+          <t>365594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264300</t>
+          <t>263009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277441</t>
+          <t>277182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616947</t>
+          <t>616510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640389</t>
+          <t>639551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84063</t>
+          <t>85698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125061</t>
+          <t>127442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>50975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120345</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167765</t>
+          <t>167400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1864456</t>
+          <t>1862075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1905454</t>
+          <t>1903819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1093784</t>
+          <t>1093292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1118134</t>
+          <t>1117295</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2966019</t>
+          <t>2966384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3013439</t>
+          <t>3015802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>13894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29012</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>224952</t>
+          <t>237478</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214945</t>
+          <t>227413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231769</t>
+          <t>244617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,27 +5685,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>291431</t>
+          <t>311523</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280936</t>
+          <t>301527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>298100</t>
+          <t>318784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243957</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243957</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243957</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56661</t>
+          <t>63311</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40980</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79643</t>
+          <t>86313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>81940</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47026</t>
+          <t>61631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96203</t>
+          <t>102263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>928232</t>
+          <t>982425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>905250</t>
+          <t>959423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>943913</t>
+          <t>998472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>693978</t>
+          <t>539995</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>681630</t>
+          <t>528100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>702766</t>
+          <t>547356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1622211</t>
+          <t>1522420</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1597140</t>
+          <t>1502097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1646317</t>
+          <t>1542729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>984893</t>
+          <t>1045736</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>984893</t>
+          <t>1045736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>984893</t>
+          <t>1045736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>708450</t>
+          <t>558624</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>708450</t>
+          <t>558624</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>708450</t>
+          <t>558624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1693343</t>
+          <t>1604360</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1693343</t>
+          <t>1604360</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1693343</t>
+          <t>1604360</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>36571</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43881</t>
+          <t>51061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>322184</t>
+          <t>343188</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311679</t>
+          <t>331400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329885</t>
+          <t>351386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>237009</t>
+          <t>258089</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228756</t>
+          <t>248518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241366</t>
+          <t>264090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>559192</t>
+          <t>601277</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546542</t>
+          <t>586787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>568827</t>
+          <t>611912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>269819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>269819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>269819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>590423</t>
+          <t>637848</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>590423</t>
+          <t>637848</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>590423</t>
+          <t>637848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78868</t>
+          <t>90313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122793</t>
+          <t>137829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90399</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>167768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1475369</t>
+          <t>1563090</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1450311</t>
+          <t>1534447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1494236</t>
+          <t>1581963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>997466</t>
+          <t>872130</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984560</t>
+          <t>855584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1009602</t>
+          <t>880932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2472835</t>
+          <t>2435219</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2443279</t>
+          <t>2407884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2504658</t>
+          <t>2458190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1573104</t>
+          <t>1672276</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1573104</t>
+          <t>1672276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1573104</t>
+          <t>1672276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1021953</t>
+          <t>903377</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1021953</t>
+          <t>903377</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1021953</t>
+          <t>903377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2595057</t>
+          <t>2575652</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2595057</t>
+          <t>2575652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2595057</t>
+          <t>2575652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
